--- a/docs/downloads/Stage 6 - Evaluate.xlsx
+++ b/docs/downloads/Stage 6 - Evaluate.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Agent correctly detected the Slack error, recorded score: "Unknown" for sentiment, and flagged the gap in the report. The synthesis node handled the missing dimension without crashing — health score was based on tickets and usage only, with an explicit caveat. Report included the line "Sentiment data was unavailable for this period" in the Sentiment section. No silent omission, no hallucinated data.</t>
+          <t>Agent correctly detected the Slack error, recorded score: "Unknown" for sentiment, and flagged the gap in the report. The synthesis action handled the missing dimension without crashing — health score was based on tickets and usage only, with an explicit caveat. Report included the line "Sentiment data was unavailable for this period" in the Sentiment section. No silent omission, no hallucinated data.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>The explicit "Sentiment data was unavailable for this period" line in the report is exactly right — transparent about what is missing without over-qualifying the rest of the analysis. The error handling in the fetch_slack_threads tool correctly caught the API error and returned an empty result with an error flag rather than propagating the exception.</t>
+          <t>The explicit "Sentiment data was unavailable for this period" line in the report is exactly right — transparent about what is missing without over-qualifying the rest of the analysis. The error handling in the Slack search tool correctly caught the API error and returned an empty result with an error flag rather than propagating the exception.</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>The agent cannot represent per-product divergence because the state schema has one usage_analysis field — this is a structural limitation, not an analysis error. The USAGE_ANALYSIS_PROMPT analysed the data it received and produced a reasonable single-score assessment given the combined input. The problem is that Scope Step 7 describes a single "Assess product engagement" step with no per-product dimension. The blended report would not trigger the needed action — a CSD reading "Needs Attention" with generic recommendations would miss the critical Analytics Dashboard decline that requires immediate intervention.</t>
+          <t>The agent cannot represent per-product divergence because the memory schema has one usage_analysis field — this is a structural limitation, not an analysis error. The USAGE_ANALYSIS_PROMPT analysed the data it received and produced a reasonable single-score assessment given the combined input. The problem is that Scope Step 7 describes a single "Assess product engagement" step with no per-product dimension. The blended report would not trigger the needed action — a CSM reading "Needs Attention" with generic recommendations would miss the critical Analytics Dashboard decline that requires immediate intervention.</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>State schema has no per-product analysis field (one usage_analysis dict for all products). Scope Step 7 assumes single-product accounts. analyse_health node makes one usage LLM call with all metrics combined. Blended averages (31.5% DAU/MAU, 50% adoption) mask per-product divergence. Generic recommendations ("monitor usage trends") instead of product-specific actions ("immediate Analytics Dashboard adoption intervention"). Report lacks per-product sections — one blended paragraph instead.</t>
+          <t>Memory schema has no per-product analysis field (one usage_analysis dict for all products). Scope Step 7 assumes single-product accounts. analyse_health action makes one usage LLM call with all metrics combined. Blended averages (31.5% DAU/MAU, 50% adoption) mask per-product divergence. Generic recommendations ("monitor usage trends") instead of product-specific actions ("immediate Analytics Dashboard adoption intervention"). Report lacks per-product sections — one blended paragraph instead.</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Root cause traced through systematic elimination of four layers: Tool ✓ (fetch_usage_metrics returned correct data for both products), Prompt ✓ (USAGE_ANALYSIS_PROMPT produced a reasonable single-score assessment given the combined data it received), Graph — partial (analyse_health makes one usage LLM call, but this is a consequence of the deeper problem), Scope ✗ (Step 7 has no per-product dimension). Fixed in Iteration 2 via cross-stage cascade: updated Scope Step 7 (per-product output and decision logic), Design state schema (added usage_analysis_by_product), Build analyse_health node (per-product loop + rollup) and prompts (USAGE_ANALYSIS_PROMPT, new USAGE_ROLLUP_PROMPT, SYNTHESIS_PROMPT). After fix, TC5 re-tested as Pass with separate product sections and product-specific recommendations.</t>
+          <t>Root cause traced through systematic elimination of four layers: Tool ✓ (usage metrics tool returned correct data for both products), Prompt ✓ (USAGE_ANALYSIS_PROMPT produced a reasonable single-score assessment given the combined data it received), Flow — partial (analyse_health makes one usage LLM call, but this is a consequence of the deeper problem), Scope ✗ (Step 7 has no per-product dimension). Fixed in Iteration 2 via cross-stage cascade: updated Scope Step 7 (per-product output and decision logic), Design memory schema (added usage_analysis_by_product), Build analyse_health action (per-product loop + rollup) and prompts (USAGE_ANALYSIS_PROMPT, new USAGE_ROLLUP_PROMPT, SYNTHESIS_PROMPT). After fix, TC5 re-tested as Pass with separate product sections and product-specific recommendations.</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Robustness was strong from the initial build. The error handling patterns established in Stage 5 (try/except with interrupt fallback, explicit Unknown/No Data markers) worked as designed. The per-product fix in Iteration 2 also handles the edge case where usage_data has no products key (falls back to single-product path).</t>
+          <t>Robustness was strong from the initial build. The error handling patterns established in Stage 5 (try/except with HIL-checkpoint fallback, explicit Unknown/No Data markers) worked as designed. The per-product fix in Iteration 2 also handles the edge case where usage_data has no products key (falls back to single-product path).</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Track the size of human edits at each checkpoint across all test cases. Categories: none, minor tweaks (wording), significant corrections (substance), complete rewrite. If edits are consistently none/minor, the checkpoint may be unnecessary. If edits are consistently significant/rewrite, the preceding node needs improvement.</t>
+          <t>Track the size of human edits at each checkpoint across all test cases. Categories: none, minor tweaks (wording), significant corrections (substance), complete rewrite. If edits are consistently none/minor, the checkpoint may be unnecessary. If edits are consistently significant/rewrite, the preceding action needs improvement.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Both HIL checkpoints produce mostly none/minor edits (indicating the preceding nodes are doing their job), with occasional significant corrections caught before they reach the final output. Checkpoints should add value without requiring routine rewrites.</t>
+          <t>Both HIL checkpoints produce mostly none/minor edits (indicating the preceding actions are doing their job), with occasional significant corrections caught before they reach the final output. Checkpoints should add value without requiring routine rewrites.</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1316,27 +1316,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Did the agent take the correct path through the graph — right node sequence, no unnecessary loops, no skipped steps? Did it reach the right output via the right process, not just by coincidence?</t>
+          <t>Did the agent take the correct path through the flow — right action sequence, no unnecessary loops, no skipped steps? Did it reach the right output via the right process, not just by coincidence?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Define expected node sequences for each test case and compare against actual execution order via traces (LangSmith or manual logging). Flag cases where the agent reached the correct output via an inefficient or incorrect path — e.g., unnecessary loops, skipped data sources, or hitting a HIL checkpoint that should have been automated.</t>
+          <t>Define expected action sequences for each test case and compare against actual execution order via traces (your platform's tracing/observability tool, or manual logging). Flag cases where the agent reached the correct output via an inefficient or incorrect path — e.g., unnecessary loops, skipped data sources, or hitting a HIL checkpoint that should have been automated.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4/5 test cases followed expected node sequence. TC1, TC3, TC4: correct sequence (fetch_data → analyse_health → hil_review_analysis → synthesise → generate_report → hil_review_report). TC2: correct sequence but sentiment analysis node produced wrong severity (path correct, output wrong). TC5: correct sequence but single-pass through analyse_health was structurally inadequate for multi-product account — the path itself was wrong for this input type.</t>
+          <t>4/5 test cases followed expected action sequence. TC1, TC3, TC4: correct sequence (gather_data → analyse_health → hil_review_analysis → synthesise → generate_report → hil_review_report). TC2: correct sequence but sentiment analysis action produced wrong severity (path correct, output wrong). TC5: correct sequence but single-pass through analyse_health was structurally inadequate for multi-product account — the path itself was wrong for this input type.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5/5 test cases follow expected node sequence. TC5 now takes the per-product path: fetch_data → analyse_health (loops per product + rollup) → hil_review_analysis → synthesise → generate_report → hil_review_report. Single-product accounts (TC1–TC4) follow the original path unchanged. No unnecessary loops or skipped steps observed.</t>
+          <t>5/5 test cases follow expected action sequence. TC5 now takes the per-product path: gather_data → analyse_health (loops per product + rollup) → hil_review_analysis → synthesise → generate_report → hil_review_report. Single-product accounts (TC1–TC4) follow the original path unchanged. No unnecessary loops or skipped steps observed.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>All test cases follow the expected node sequence for their input type. No unnecessary loops, no skipped steps, no cases where the agent reaches the right output via the wrong path.</t>
+          <t>All test cases follow the expected action sequence for their input type. No unnecessary loops, no skipped steps, no cases where the agent reaches the right output via the wrong path.</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Checked each layer in order. Tool layer: fetch_slack_threads returned the correct Slack threads including the VP of Engineering's messages — data was correct and complete (Tool ✓). Prompt layer: SENTIMENT_ANALYSIS_PROMPT instructs the LLM to analyse Slack thread sentiment but gives no guidance on weighting by stakeholder role or seniority. The LLM did what the prompt asked — it treated all messages equally and produced "Needs Attention" — but the prompt did not ask for the right thing. The distinction between a frustrated VP and a frustrated junior user is material to risk assessment, and the prompt did not encode it (Prompt ✗). Graph layer check was unnecessary — failure identified at prompt layer.</t>
+          <t>Checked each layer in order. Tool layer: the Slack search tool returned the correct Slack threads including the VP of Engineering's messages — data was correct and complete (Tool ✓). Prompt layer: SENTIMENT_ANALYSIS_PROMPT instructs the LLM to analyse Slack thread sentiment but gives no guidance on weighting by stakeholder role or seniority. The LLM did what the prompt asked — it treated all messages equally and produced "Needs Attention" — but the prompt did not ask for the right thing. The distinction between a frustrated VP and a frustrated junior user is material to risk assessment, and the prompt did not encode it (Prompt ✗). Flow layer check was unnecessary — failure identified at prompt layer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>prompts.py (SENTIMENT_ANALYSIS_PROMPT)</t>
+          <t>Prompt module (SENTIMENT_ANALYSIS_PROMPT)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>TC2: Partial → Pass. Sentiment analysis now scored "Critical," citing the VP of Engineering's messages as the primary signal and noting that executive-level frustration near a renewal represents elevated churn risk. Synthesis node picked up the stronger signal. Report's sentiment section now matches the manually written version. TC1, TC3, TC4: no regression — all still Pass.</t>
+          <t>TC2: Partial → Pass. Sentiment analysis now scored "Critical," citing the VP of Engineering's messages as the primary signal and noting that executive-level frustration near a renewal represents elevated churn risk. The synthesise action picked up the stronger signal. Report's sentiment section now matches the manually written version. TC1, TC3, TC4: no regression — all still Pass.</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -1569,17 +1569,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Systematic elimination through four layers. Tool layer: fetch_usage_metrics returned correct data for both products — raw data was complete (Tool ✓). Prompt layer: USAGE_ANALYSIS_PROMPT received the combined usage data and produced a reasonable single-score assessment given the combined input — the prompt did what it was asked to do (Prompt ✓). Graph layer: analyse_health makes one usage LLM call and writes one usage_analysis dict to state — but this structure is a consequence of a deeper problem (Graph — partial). Scope layer: Step 7 in the Scope Document describes a single "Assess product engagement" step with output "Engagement assessment (healthy/at-risk/critical)" and decision logic referencing one set of metrics with no per-product dimension. The scope assumed single-product accounts, and every downstream artifact inherited that assumption (Scope ✗). Root cause: scope issue, the most consequential category because it cascades through Stages 3 → 4 → 5.</t>
+          <t>Systematic elimination through four layers. Tool layer: the usage metrics tool returned correct data for both products — raw data was complete (Tool ✓). Prompt layer: USAGE_ANALYSIS_PROMPT received the combined usage data and produced a reasonable single-score assessment given the combined input — the prompt did what it was asked to do (Prompt ✓). Flow layer: analyse_health makes one usage LLM call and writes one usage_analysis dict to memory — but this structure is a consequence of a deeper problem (Flow — partial). Scope layer: Step 7 in the Scope Document describes a single "Assess product engagement" step with output "Engagement assessment (healthy/at-risk/critical)" and decision logic referencing one set of metrics with no per-product dimension. The scope assumed single-product accounts, and every downstream artifact inherited that assumption (Scope ✗). Root cause: scope issue, the most consequential category because it cascades through Stages 3 → 4 → 5.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Cross-stage cascade — updated the affected part of each artifact in order. Stage 3 (Scope): Updated Step 7 output from "Engagement assessment (healthy/at-risk/critical)" to "Per-product engagement assessments + rollup engagement summary (healthy/at-risk/critical per product, with notation of cross-product divergence)." Added decision logic: for multi-product accounts, assess each product independently before computing rollup; flag divergence &gt; 2 rating levels. Stage 4 (Design): Added usage_analysis_by_product dict to AccountHealthState. Existing usage_analysis becomes the rollup. Updated analyse_health node spec for per-product loop. Stage 5 (Build): Updated analyse_health_node to loop over products (one LLM call per product), added usage_analysis_by_product to state, added rollup logic with USAGE_ROLLUP_PROMPT. Single-product fallback preserves existing behaviour. Updated SYNTHESIS_PROMPT with usage_by_product_json placeholder.</t>
+          <t>Cross-stage cascade — updated the affected part of each artifact in order. Stage 3 (Scope): Updated Step 7 output from "Engagement assessment (healthy/at-risk/critical)" to "Per-product engagement assessments + rollup engagement summary (healthy/at-risk/critical per product, with notation of cross-product divergence)." Added decision logic: for multi-product accounts, assess each product independently before computing rollup; flag divergence &gt; 2 rating levels. Stage 4 (Design): Added usage_analysis_by_product dict to the memory schema. Existing usage_analysis becomes the rollup. Updated analyse_health action spec for per-product loop. Stage 5 (Build): Updated analyse_health to loop over products (one LLM call per product), added usage_analysis_by_product to memory, added rollup logic with USAGE_ROLLUP_PROMPT. Single-product fallback preserves existing behaviour. Updated SYNTHESIS_PROMPT with usage_by_product_json placeholder.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>prompts.py (USAGE_ANALYSIS_PROMPT — added product_name placeholder, new USAGE_ROLLUP_PROMPT, SYNTHESIS_PROMPT — added usage_by_product_json), nodes.py (analyse_health_node — per-product loop + rollup logic), state.py (AccountHealthState — added usage_analysis_by_product field), scope document (Step 7 output and decision logic), design document (state schema and analyse_health node spec)</t>
+          <t>Prompt module (USAGE_ANALYSIS_PROMPT — added product_name placeholder, new USAGE_ROLLUP_PROMPT, SYNTHESIS_PROMPT — added usage_by_product_json), actions module (analyse_health — per-product loop + rollup logic), memory module (added usage_analysis_by_product field), scope document (Step 7 output and decision logic), design document (memory schema and analyse_health action spec)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Stage 3 (Scope): Updated Step 7 output to include per-product dimension and added decision logic for multi-product assessment and divergence flagging. Step action, input, and boundary tag (AUTOMATE/HIL) unchanged. Stage 4 (Design): Added usage_analysis_by_product field to state schema. Updated analyse_health node specification to describe per-product loop and rollup. Existing usage_analysis field retained as rollup — downstream nodes (synthesise, generate_report) that read usage_analysis continue to work unchanged.</t>
+          <t>Stage 3 (Scope): Updated Step 7 output to include per-product dimension and added decision logic for multi-product assessment and divergence flagging. Step action, input, and boundary tag (AUTOMATE/HIL) unchanged. Stage 4 (Design): Added usage_analysis_by_product field to memory schema. Updated analyse_health action specification to describe per-product loop and rollup. Existing usage_analysis field retained as rollup — downstream actions (synthesise, generate_report) that read usage_analysis continue to work unchanged.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>No critical failures — defined as wrong health scores, missed major risks, wrong conclusions that would lead to incorrect actions — in the last 3 consecutive evaluation rounds. A critical failure is one where the agent's output would cause a CSD to take the wrong action or miss a necessary intervention.</t>
+          <t>No critical failures — defined as wrong health scores, missed major risks, wrong conclusions that would lead to incorrect actions — in the last 3 consecutive evaluation rounds. A critical failure is one where the agent's output would cause a CSM to take the wrong action or miss a necessary intervention.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Checkpoint edits should be none/minor in &gt; 80% of cases (indicating the analysis node is doing its job)</t>
+          <t>Checkpoint edits should be none/minor in &gt; 80% of cases (indicating the analysis action is doing its job)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Checkpoint edits should be none/minor in &gt; 80% of cases (indicating the report generation node is doing its job)</t>
+          <t>Checkpoint edits should be none/minor in &gt; 80% of cases (indicating the report generation action is doing its job)</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
